--- a/backend/academics/tests/fixtures/schedule_import.xlsx
+++ b/backend/academics/tests/fixtures/schedule_import.xlsx
@@ -19,8 +19,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сотрудники'!$A$1:$M$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Группы'!$A$1:$G$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Предметы'!$A$1:$C$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Звонки'!$A$1:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Предметы'!$A$1:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Звонки'!$A$1:$D$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Подгруппы'!$A$1:$G$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Уроки'!$A$1:$M$1109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Допущения'!$A$1:$D$19</definedName>
@@ -4373,12 +4373,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4397,6 +4398,11 @@
           <t>Уроков в неделю (все группы)</t>
         </is>
       </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Оценивание</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -4412,6 +4418,11 @@
       <c r="C2" s="4" t="n">
         <v>11</v>
       </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -4427,6 +4438,11 @@
       <c r="C3" s="4" t="n">
         <v>20</v>
       </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -4442,6 +4458,11 @@
       <c r="C4" s="4" t="n">
         <v>178</v>
       </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>без оценок</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4457,6 +4478,11 @@
       <c r="C5" s="4" t="n">
         <v>33</v>
       </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -4472,6 +4498,11 @@
       <c r="C6" s="4" t="n">
         <v>209</v>
       </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -4487,6 +4518,11 @@
       <c r="C7" s="4" t="n">
         <v>70</v>
       </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -4502,6 +4538,11 @@
       <c r="C8" s="4" t="n">
         <v>40</v>
       </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -4517,6 +4558,11 @@
       <c r="C9" s="4" t="n">
         <v>23</v>
       </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -4532,6 +4578,11 @@
       <c r="C10" s="4" t="n">
         <v>30</v>
       </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -4547,6 +4598,11 @@
       <c r="C11" s="4" t="n">
         <v>10</v>
       </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -4562,6 +4618,11 @@
       <c r="C12" s="4" t="n">
         <v>20</v>
       </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -4577,6 +4638,11 @@
       <c r="C13" s="4" t="n">
         <v>69</v>
       </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -4592,6 +4658,11 @@
       <c r="C14" s="4" t="n">
         <v>29</v>
       </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -4607,6 +4678,11 @@
       <c r="C15" s="4" t="n">
         <v>31</v>
       </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>без оценок</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -4622,6 +4698,11 @@
       <c r="C16" s="4" t="n">
         <v>59</v>
       </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -4637,6 +4718,11 @@
       <c r="C17" s="4" t="n">
         <v>43</v>
       </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -4652,6 +4738,11 @@
       <c r="C18" s="4" t="n">
         <v>6</v>
       </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -4667,6 +4758,11 @@
       <c r="C19" s="4" t="n">
         <v>55</v>
       </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>без оценок</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -4682,6 +4778,11 @@
       <c r="C20" s="4" t="n">
         <v>17</v>
       </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -4697,6 +4798,11 @@
       <c r="C21" s="4" t="n">
         <v>23</v>
       </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -4712,6 +4818,11 @@
       <c r="C22" s="4" t="n">
         <v>30</v>
       </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -4727,6 +4838,11 @@
       <c r="C23" s="4" t="n">
         <v>40</v>
       </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -4742,6 +4858,11 @@
       <c r="C24" s="4" t="n">
         <v>50</v>
       </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -4757,9 +4878,14 @@
       <c r="C25" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>ФО, СОР, СОЧ</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C25"/>
+  <autoFilter ref="A1:D25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4770,7 +4896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4966,20 +5092,20 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8–9</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:40</t>
         </is>
       </c>
     </row>
@@ -4990,16 +5116,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:55</t>
         </is>
       </c>
     </row>
@@ -5010,16 +5136,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:40</t>
         </is>
       </c>
     </row>
@@ -5030,16 +5156,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:25</t>
         </is>
       </c>
     </row>
@@ -5049,19 +5175,17 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>обед</t>
-        </is>
+      <c r="B14" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:10</t>
         </is>
       </c>
     </row>
@@ -5071,17 +5195,19 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>5</v>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>обед</t>
+        </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:55</t>
         </is>
       </c>
     </row>
@@ -5092,16 +5218,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:40</t>
         </is>
       </c>
     </row>
@@ -5112,16 +5238,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:25</t>
         </is>
       </c>
     </row>
@@ -5132,36 +5258,36 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>16:55</t>
         </is>
       </c>
     </row>
@@ -5172,16 +5298,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:55</t>
         </is>
       </c>
     </row>
@@ -5192,16 +5318,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:40</t>
         </is>
       </c>
     </row>
@@ -5212,16 +5338,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:25</t>
         </is>
       </c>
     </row>
@@ -5232,16 +5358,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:10</t>
         </is>
       </c>
     </row>
@@ -5251,19 +5377,17 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>обед</t>
-        </is>
+      <c r="B24" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:55</t>
         </is>
       </c>
     </row>
@@ -5273,22 +5397,44 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>обед</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>14:45</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>15:25</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D25"/>
+  <autoFilter ref="A1:D26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/backend/academics/tests/fixtures/schedule_import.xlsx
+++ b/backend/academics/tests/fixtures/schedule_import.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Звонки'!$A$1:$D$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Подгруппы'!$A$1:$G$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Уроки'!$A$1:$M$1109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Допущения'!$A$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Допущения'!$A$1:$D$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>YALE, PRINCETON, HONG KONG</t>
+          <t>CHICAGO, TOKYO, SEOUL</t>
         </is>
       </c>
       <c r="I41" s="4" t="n">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>CHICAGO, TOKYO, SEOUL</t>
+          <t>YALE, PRINCETON, HONG KONG</t>
         </is>
       </c>
       <c r="I42" s="4" t="n">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Тестова40 Имя40 Отчество40</t>
+          <t>Тестова41 Имя41 Отчество41</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>С40</t>
+          <t>С41</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Тестова40 Имя40 Отчество40</t>
+          <t>Тестова41 Имя41 Отчество41</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>С40</t>
+          <t>С41</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Тестова40 Имя40 Отчество40</t>
+          <t>Тестова41 Имя41 Отчество41</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>С40</t>
+          <t>С41</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Тестова41 Имя41 Отчество41</t>
+          <t>Тестова40 Имя40 Отчество40</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>С41</t>
+          <t>С40</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Тестова41 Имя41 Отчество41</t>
+          <t>Тестова40 Имя40 Отчество40</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>С41</t>
+          <t>С40</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Тестова41 Имя41 Отчество41</t>
+          <t>Тестова40 Имя40 Отчество40</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>С41</t>
+          <t>С40</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -34237,12 +34237,12 @@
       </c>
       <c r="I528" s="4" t="inlineStr">
         <is>
-          <t>Тестова40 Имя40 Отчество40</t>
+          <t>Тестова41 Имя41 Отчество41</t>
         </is>
       </c>
       <c r="J528" s="4" t="inlineStr">
         <is>
-          <t>С40</t>
+          <t>С41</t>
         </is>
       </c>
       <c r="K528" s="4" t="inlineStr">
@@ -38623,12 +38623,12 @@
       </c>
       <c r="I614" s="4" t="inlineStr">
         <is>
-          <t>Тестова40 Имя40 Отчество40</t>
+          <t>Тестова41 Имя41 Отчество41</t>
         </is>
       </c>
       <c r="J614" s="4" t="inlineStr">
         <is>
-          <t>С40</t>
+          <t>С41</t>
         </is>
       </c>
       <c r="K614" s="4" t="inlineStr">
@@ -42244,12 +42244,12 @@
       </c>
       <c r="I685" s="4" t="inlineStr">
         <is>
-          <t>Тестова40 Имя40 Отчество40</t>
+          <t>Тестова41 Имя41 Отчество41</t>
         </is>
       </c>
       <c r="J685" s="4" t="inlineStr">
         <is>
-          <t>С40</t>
+          <t>С41</t>
         </is>
       </c>
       <c r="K685" s="4" t="inlineStr">
@@ -51260,12 +51260,12 @@
       </c>
       <c r="I861" s="4" t="inlineStr">
         <is>
-          <t>Тестова41 Имя41 Отчество41</t>
+          <t>Тестова40 Имя40 Отчество40</t>
         </is>
       </c>
       <c r="J861" s="4" t="inlineStr">
         <is>
-          <t>С41</t>
+          <t>С40</t>
         </is>
       </c>
       <c r="K861" s="4" t="inlineStr">
@@ -56714,12 +56714,12 @@
       </c>
       <c r="I967" s="4" t="inlineStr">
         <is>
-          <t>Тестова41 Имя41 Отчество41</t>
+          <t>Тестова40 Имя40 Отчество40</t>
         </is>
       </c>
       <c r="J967" s="4" t="inlineStr">
         <is>
-          <t>С41</t>
+          <t>С40</t>
         </is>
       </c>
       <c r="K967" s="4" t="inlineStr">
@@ -58405,12 +58405,12 @@
       </c>
       <c r="I1000" s="4" t="inlineStr">
         <is>
-          <t>Тестова41 Имя41 Отчество41</t>
+          <t>Тестова40 Имя40 Отчество40</t>
         </is>
       </c>
       <c r="J1000" s="4" t="inlineStr">
         <is>
-          <t>С41</t>
+          <t>С40</t>
         </is>
       </c>
       <c r="K1000" s="4" t="inlineStr">
@@ -64024,7 +64024,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D19"/>
+  <autoFilter ref="A1:D20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>